--- a/Result/profitability/8054.xlsx
+++ b/Result/profitability/8054.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6462500000000001</v>
+        <v>-0.6062500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>27.32625</v>
+        <v>25.01625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4575</v>
+        <v>-0.33</v>
       </c>
       <c r="N3" t="n">
-        <v>27.445</v>
+        <v>26.47375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2</v>
+        <v>-0.14125</v>
       </c>
       <c r="N4" t="n">
-        <v>28.63375</v>
+        <v>25.57125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06375000000000006</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="N5" t="n">
-        <v>27.07125</v>
+        <v>25.37625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06874999999999995</v>
+        <v>0.17125</v>
       </c>
       <c r="N6" t="n">
-        <v>27.895</v>
+        <v>27.56125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2725</v>
+        <v>0.3412499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>30.03375</v>
+        <v>30.07</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5287500000000001</v>
+        <v>0.50125</v>
       </c>
       <c r="N8" t="n">
-        <v>33.03375</v>
+        <v>33.18125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.37</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5762499999999999</v>
+        <v>0.57625</v>
       </c>
       <c r="N9" t="n">
         <v>35.32125</v>
@@ -1645,7 +1645,7 @@
         <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="N10" t="n">
         <v>35.725</v>
@@ -1772,7 +1772,7 @@
         <v>0.91</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6537499999999999</v>
+        <v>0.6537500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>36.06875</v>
@@ -1899,7 +1899,7 @@
         <v>0.85</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6587500000000001</v>
+        <v>0.6587499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>36.39375</v>
@@ -2029,7 +2029,7 @@
         <v>0.68375</v>
       </c>
       <c r="N13" t="n">
-        <v>37.11125</v>
+        <v>37.11125000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8054</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D75" t="n">
+        <v>986</v>
+      </c>
+      <c r="E75" t="n">
+        <v>200</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-119</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-10.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>51</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.6537500000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.08875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.179999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07506361323155208</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6515151515151515</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-13.56</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4451739986868024</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
